--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8942-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8942-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39BD98EF-2D9E-4B43-B79A-B2AE5E47DC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B8EE646-AC78-4932-85E2-2351E6DABDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{EFBA07D1-BD07-45DE-88F8-8D09F1BABD20}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{79D54431-863B-4545-B056-4A48B2F1B94A}"/>
   </bookViews>
   <sheets>
     <sheet name="8942-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1520,26 +1520,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3387B14-3113-43DA-A0A9-A6F0C2B58708}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4237A456-3733-466E-AF20-EC2A018A7519}">
   <dimension ref="A1:X41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1729,7 +1729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2024</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2023</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>5.91</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2022</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2021</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2020</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2019</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2018</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2017</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2016</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>9.0399999999999991</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2015</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2014</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2013</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2012</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2011</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2010</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2009</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2008</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2007</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2006</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2005</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2004</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2003</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2002</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2001</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2000</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35" t="s">
         <v>61</v>
       </c>
